--- a/ministry/2026_사역신청_부서확인양식.xlsx
+++ b/ministry/2026_사역신청_부서확인양식.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="임명직 전용 부서" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$K$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$M$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -565,54 +565,61 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3. H열 '확정 표기명'에 2026년 최종 명칭을 적어 주세요(그대로면 D열과 동일하게 적어도 됩니다).</t>
+          <t>3. F열 '사역 시간·요일'과 G열 '하는 일'을 채워 주세요 — 이 둘은 모든 행이 비어 있습니다(2026-09-07 추가). 성도가 앱에서 사역을 고를 때 이름만 보고는 판단할 수 없어(예: 오병이어 1팀·2팀이 무엇이 다른지) 이번에 함께 걷습니다. 짧게만 적어 주셔도 됩니다(예: '매주 화 오전 10시', '주일 예배 전 주차 안내').</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4. I열 '변경여부'는 목록에서 유지 / 이름 수정 / 신설 / 폐지 중 하나를 골라 주세요.</t>
+          <t>4. J열 '확정 표기명'에 2026년 최종 명칭을 적어 주세요(그대로면 D열과 동일하게 적어도 됩니다).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5. J열에 확인하신 분 성함을, K열에는 그 밖에 전달할 내용을 적어 주세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+          <t>5. K열 '변경여부'는 목록에서 유지 / 이름 수정 / 신설 / 폐지 중 하나를 골라 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>6. L열에 확인하신 분 성함을, M열에는 그 밖에 전달할 내용을 적어 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>색이 칠해진 자리</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>▨ 분홍색 행 — 두 원본 문서(인사표·신청서)의 표기가 서로 달라 어느 쪽이 맞는지 확인이 필요한 자리입니다. G열 '확인이 필요한 사유'에 무엇이 다른지 적어 두었습니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>▨ 회색 행 — 신청이 아니라 지명으로 맡는 임명직입니다. 성도가 직접 신청하지 않으므로 앱의 신청 목록에는 넣지 않습니다. 이름이 맞는지만 확인해 주세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="2" t="inlineStr">
+          <t>▨ 분홍색 행 — 두 원본 문서(인사표·신청서)의 표기가 서로 달라 어느 쪽이 맞는지 확인이 필요한 자리입니다. I열 '확인이 필요한 사유'에 무엇이 다른지 적어 두었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>▨ 회색 행 — 신청이 아니라 지명으로 맡는 임명직입니다. 성도가 직접 신청하지 않으므로 앱의 신청 목록에는 넣지 않습니다. 이름이 맞는지만 확인해 주세요(시간·요일은 안 채우셔도 됩니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>임명직만 있어 개별 사역팀이 없는 부서(M-12부·재정부·감사위원회 등)는 「임명직 전용 부서」 시트에 따로 안내했습니다.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>문의: 제자양육부 신앙운동팀</t>
         </is>
@@ -629,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -637,12 +644,14 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -673,30 +682,40 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>사역 시간·요일 (부서 기입)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>하는 일 — 한 줄 (부서 기입)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
           <t>하위 선택 안내</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>확인이 필요한 사유</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>확정 표기명 (부서 기입)</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>변경여부</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>담당자 확인 (성명)</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -725,9 +744,11 @@
       <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
       <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="6" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr"/>
+      <c r="M2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -752,9 +773,11 @@
       <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -779,9 +802,11 @@
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -807,16 +832,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -842,16 +869,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -877,16 +906,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -912,16 +943,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -950,9 +983,11 @@
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -981,9 +1016,11 @@
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1012,9 +1049,11 @@
       <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr"/>
-      <c r="K11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="6" t="inlineStr"/>
+      <c r="M11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1043,9 +1082,11 @@
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1074,9 +1115,11 @@
       <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="6" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1105,9 +1148,11 @@
       <c r="F14" s="8" t="inlineStr"/>
       <c r="G14" s="8" t="inlineStr"/>
       <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
+      <c r="J14" s="8" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1136,9 +1181,11 @@
       <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1167,9 +1214,11 @@
       <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
       <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="8" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1198,9 +1247,11 @@
       <c r="F17" s="8" t="inlineStr"/>
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr"/>
-      <c r="K17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1229,9 +1280,11 @@
       <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
+      <c r="J18" s="8" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1260,9 +1313,11 @@
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1287,9 +1342,11 @@
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
-      <c r="J20" s="9" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1314,9 +1371,11 @@
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1341,9 +1400,11 @@
       <c r="F22" s="8" t="inlineStr"/>
       <c r="G22" s="8" t="inlineStr"/>
       <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
+      <c r="J22" s="8" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1368,9 +1429,11 @@
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -1395,9 +1458,11 @@
       <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="6" t="inlineStr"/>
-      <c r="K24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1419,16 +1484,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>다른 찬양대와 겸직 가능한 유일한 예외</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="6" t="inlineStr"/>
+      <c r="M25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1453,9 +1520,11 @@
       <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="8" t="inlineStr"/>
       <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1480,9 +1549,11 @@
       <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="8" t="inlineStr"/>
       <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -1507,9 +1578,11 @@
       <c r="F28" s="8" t="inlineStr"/>
       <c r="G28" s="8" t="inlineStr"/>
       <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="6" t="inlineStr"/>
-      <c r="K28" s="8" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
+      <c r="J28" s="8" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1534,9 +1607,11 @@
       <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="8" t="inlineStr"/>
       <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="6" t="inlineStr"/>
-      <c r="K29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1561,9 +1636,11 @@
       <c r="F30" s="8" t="inlineStr"/>
       <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="6" t="inlineStr"/>
-      <c r="K30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1588,9 +1665,11 @@
       <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="8" t="inlineStr"/>
       <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="6" t="inlineStr"/>
+      <c r="M31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -1615,9 +1694,11 @@
       <c r="F32" s="8" t="inlineStr"/>
       <c r="G32" s="8" t="inlineStr"/>
       <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
+      <c r="J32" s="8" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1642,9 +1723,11 @@
       <c r="F33" s="8" t="inlineStr"/>
       <c r="G33" s="8" t="inlineStr"/>
       <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1669,9 +1752,11 @@
       <c r="F34" s="8" t="inlineStr"/>
       <c r="G34" s="8" t="inlineStr"/>
       <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr"/>
-      <c r="K34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="8" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1696,9 +1781,11 @@
       <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="8" t="inlineStr"/>
       <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr"/>
-      <c r="J35" s="6" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -1723,9 +1810,11 @@
       <c r="F36" s="8" t="inlineStr"/>
       <c r="G36" s="8" t="inlineStr"/>
       <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
-      <c r="J36" s="6" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr"/>
+      <c r="J36" s="8" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr"/>
+      <c r="M36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -1750,9 +1839,11 @@
       <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
       <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="6" t="inlineStr"/>
-      <c r="J37" s="6" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr"/>
+      <c r="M37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -1777,9 +1868,11 @@
       <c r="F38" s="8" t="inlineStr"/>
       <c r="G38" s="8" t="inlineStr"/>
       <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
-      <c r="J38" s="6" t="inlineStr"/>
-      <c r="K38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr"/>
+      <c r="M38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -1804,9 +1897,11 @@
       <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="6" t="inlineStr"/>
-      <c r="K39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
+      <c r="L39" s="6" t="inlineStr"/>
+      <c r="M39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -1831,9 +1926,11 @@
       <c r="F40" s="8" t="inlineStr"/>
       <c r="G40" s="8" t="inlineStr"/>
       <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
+      <c r="J40" s="8" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr"/>
+      <c r="M40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -1858,9 +1955,11 @@
       <c r="F41" s="8" t="inlineStr"/>
       <c r="G41" s="8" t="inlineStr"/>
       <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="6" t="inlineStr"/>
-      <c r="K41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -1885,9 +1984,11 @@
       <c r="F42" s="8" t="inlineStr"/>
       <c r="G42" s="8" t="inlineStr"/>
       <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="6" t="inlineStr"/>
-      <c r="K42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
+      <c r="J42" s="8" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr"/>
+      <c r="M42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -1912,9 +2013,11 @@
       <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="8" t="inlineStr"/>
       <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
-      <c r="J43" s="6" t="inlineStr"/>
-      <c r="K43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -1939,9 +2042,11 @@
       <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="8" t="inlineStr"/>
       <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr"/>
-      <c r="J44" s="6" t="inlineStr"/>
-      <c r="K44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -1966,9 +2071,11 @@
       <c r="F45" s="8" t="inlineStr"/>
       <c r="G45" s="8" t="inlineStr"/>
       <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
-      <c r="J45" s="6" t="inlineStr"/>
-      <c r="K45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr"/>
+      <c r="M45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -1993,9 +2100,11 @@
       <c r="F46" s="8" t="inlineStr"/>
       <c r="G46" s="8" t="inlineStr"/>
       <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="6" t="inlineStr"/>
-      <c r="K46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="8" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr"/>
+      <c r="M46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -2020,9 +2129,11 @@
       <c r="F47" s="8" t="inlineStr"/>
       <c r="G47" s="8" t="inlineStr"/>
       <c r="H47" s="8" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="6" t="inlineStr"/>
-      <c r="K47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr"/>
+      <c r="M47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
@@ -2047,9 +2158,11 @@
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="10" t="inlineStr"/>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr"/>
-      <c r="K48" s="10" t="inlineStr"/>
+      <c r="I48" s="10" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr"/>
+      <c r="K48" s="9" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr"/>
+      <c r="M48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
@@ -2072,15 +2185,17 @@
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr"/>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr"/>
+      <c r="H49" s="12" t="inlineStr"/>
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>조직표에는 회계(최현희)가 있으나 신청서 양식에는 없음 — 임명직인지, 신청서 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr"/>
-      <c r="K49" s="12" t="inlineStr"/>
+      <c r="J49" s="12" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr"/>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -2105,9 +2220,11 @@
       <c r="F50" s="8" t="inlineStr"/>
       <c r="G50" s="8" t="inlineStr"/>
       <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="6" t="inlineStr"/>
-      <c r="K50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
+      <c r="J50" s="8" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -2132,9 +2249,11 @@
       <c r="F51" s="8" t="inlineStr"/>
       <c r="G51" s="8" t="inlineStr"/>
       <c r="H51" s="8" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr"/>
-      <c r="J51" s="6" t="inlineStr"/>
-      <c r="K51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
+      <c r="J51" s="8" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -2159,9 +2278,11 @@
       <c r="F52" s="8" t="inlineStr"/>
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="6" t="inlineStr"/>
-      <c r="K52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="inlineStr"/>
+      <c r="J52" s="8" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -2186,9 +2307,11 @@
       <c r="F53" s="8" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
+      <c r="J53" s="8" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -2213,9 +2336,11 @@
       <c r="F54" s="8" t="inlineStr"/>
       <c r="G54" s="8" t="inlineStr"/>
       <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="6" t="inlineStr"/>
-      <c r="K54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="8" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2240,9 +2365,11 @@
       <c r="F55" s="8" t="inlineStr"/>
       <c r="G55" s="8" t="inlineStr"/>
       <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr"/>
-      <c r="K55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr"/>
+      <c r="J55" s="8" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -2268,16 +2395,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr"/>
+      <c r="G56" s="8" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>행복전도대 요일 중 하나 이상 신청</t>
         </is>
       </c>
-      <c r="G56" s="8" t="inlineStr"/>
-      <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="6" t="inlineStr"/>
-      <c r="K56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="inlineStr"/>
+      <c r="J56" s="8" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2303,16 +2432,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr"/>
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>행복전도대 요일 중 하나 이상 신청</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr"/>
-      <c r="I57" s="6" t="inlineStr"/>
-      <c r="J57" s="6" t="inlineStr"/>
-      <c r="K57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr"/>
+      <c r="J57" s="8" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
+      <c r="L57" s="6" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -2337,9 +2468,11 @@
       <c r="F58" s="8" t="inlineStr"/>
       <c r="G58" s="8" t="inlineStr"/>
       <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="6" t="inlineStr"/>
-      <c r="K58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2364,9 +2497,11 @@
       <c r="F59" s="8" t="inlineStr"/>
       <c r="G59" s="8" t="inlineStr"/>
       <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="6" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="8" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="6" t="inlineStr"/>
+      <c r="M59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -2391,9 +2526,11 @@
       <c r="F60" s="8" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr"/>
-      <c r="K60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr"/>
+      <c r="M60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -2418,9 +2555,11 @@
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="6" t="inlineStr"/>
-      <c r="K61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr"/>
+      <c r="J61" s="8" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr"/>
+      <c r="M61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -2445,9 +2584,11 @@
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="6" t="inlineStr"/>
-      <c r="J62" s="6" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="8" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -2472,9 +2613,11 @@
       <c r="F63" s="8" t="inlineStr"/>
       <c r="G63" s="8" t="inlineStr"/>
       <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="6" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -2499,9 +2642,11 @@
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr"/>
-      <c r="J64" s="6" t="inlineStr"/>
-      <c r="K64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr"/>
+      <c r="J64" s="8" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -2526,9 +2671,11 @@
       <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="6" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -2553,9 +2700,11 @@
       <c r="F66" s="8" t="inlineStr"/>
       <c r="G66" s="8" t="inlineStr"/>
       <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="6" t="inlineStr"/>
-      <c r="J66" s="6" t="inlineStr"/>
-      <c r="K66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr"/>
+      <c r="J66" s="8" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr"/>
+      <c r="L66" s="6" t="inlineStr"/>
+      <c r="M66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -2580,9 +2729,11 @@
       <c r="F67" s="8" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr"/>
       <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr"/>
+      <c r="L67" s="6" t="inlineStr"/>
+      <c r="M67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -2605,15 +2756,17 @@
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr"/>
-      <c r="G68" s="12" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr"/>
+      <c r="H68" s="12" t="inlineStr"/>
+      <c r="I68" s="12" t="inlineStr">
         <is>
           <t>신청서에만 있고 조직표(인사표)에는 없음 — 신설 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="H68" s="12" t="inlineStr"/>
-      <c r="I68" s="11" t="inlineStr"/>
-      <c r="J68" s="11" t="inlineStr"/>
-      <c r="K68" s="12" t="inlineStr"/>
+      <c r="J68" s="12" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr"/>
+      <c r="M68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -2636,15 +2789,17 @@
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr"/>
-      <c r="G69" s="12" t="inlineStr">
+      <c r="G69" s="12" t="inlineStr"/>
+      <c r="H69" s="12" t="inlineStr"/>
+      <c r="I69" s="12" t="inlineStr">
         <is>
           <t>신청서에만 있고 조직표(인사표)에는 없음 — 신설 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="H69" s="12" t="inlineStr"/>
-      <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="11" t="inlineStr"/>
-      <c r="K69" s="12" t="inlineStr"/>
+      <c r="J69" s="12" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -2670,16 +2825,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>주일찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="6" t="inlineStr"/>
-      <c r="K70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
+      <c r="L70" s="6" t="inlineStr"/>
+      <c r="M70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -2705,16 +2862,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>주일찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="6" t="inlineStr"/>
-      <c r="K71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr"/>
+      <c r="L71" s="6" t="inlineStr"/>
+      <c r="M71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -2740,16 +2899,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
+      <c r="F72" s="8" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>주일찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="6" t="inlineStr"/>
-      <c r="K72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr"/>
+      <c r="J72" s="8" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
+      <c r="L72" s="6" t="inlineStr"/>
+      <c r="M72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -2775,16 +2936,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="F73" s="8" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>수요찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="6" t="inlineStr"/>
-      <c r="J73" s="6" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
+      <c r="L73" s="6" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -2810,16 +2973,18 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>수요찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="6" t="inlineStr"/>
-      <c r="K74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr"/>
+      <c r="J74" s="8" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr"/>
+      <c r="M74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -2844,9 +3009,11 @@
       <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="6" t="inlineStr"/>
-      <c r="K75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
+      <c r="L75" s="6" t="inlineStr"/>
+      <c r="M75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -2871,9 +3038,11 @@
       <c r="F76" s="8" t="inlineStr"/>
       <c r="G76" s="8" t="inlineStr"/>
       <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="6" t="inlineStr"/>
-      <c r="J76" s="6" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr"/>
+      <c r="M76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -2896,15 +3065,17 @@
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr"/>
-      <c r="G77" s="12" t="inlineStr">
+      <c r="G77" s="12" t="inlineStr"/>
+      <c r="H77" s="12" t="inlineStr"/>
+      <c r="I77" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 임명직으로 볼지 확인 필요</t>
         </is>
       </c>
-      <c r="H77" s="12" t="inlineStr"/>
-      <c r="I77" s="11" t="inlineStr"/>
-      <c r="J77" s="11" t="inlineStr"/>
-      <c r="K77" s="12" t="inlineStr"/>
+      <c r="J77" s="12" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -2927,15 +3098,17 @@
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr"/>
-      <c r="G78" s="12" t="inlineStr">
+      <c r="G78" s="12" t="inlineStr"/>
+      <c r="H78" s="12" t="inlineStr"/>
+      <c r="I78" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 임명직으로 볼지 확인 필요</t>
         </is>
       </c>
-      <c r="H78" s="12" t="inlineStr"/>
-      <c r="I78" s="11" t="inlineStr"/>
-      <c r="J78" s="11" t="inlineStr"/>
-      <c r="K78" s="12" t="inlineStr"/>
+      <c r="J78" s="12" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr"/>
+      <c r="L78" s="11" t="inlineStr"/>
+      <c r="M78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
@@ -2958,15 +3131,17 @@
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr"/>
-      <c r="G79" s="12" t="inlineStr">
+      <c r="G79" s="12" t="inlineStr"/>
+      <c r="H79" s="12" t="inlineStr"/>
+      <c r="I79" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 신청 대상 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="H79" s="12" t="inlineStr"/>
-      <c r="I79" s="11" t="inlineStr"/>
-      <c r="J79" s="11" t="inlineStr"/>
-      <c r="K79" s="12" t="inlineStr"/>
+      <c r="J79" s="12" t="inlineStr"/>
+      <c r="K79" s="11" t="inlineStr"/>
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -2989,15 +3164,17 @@
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr"/>
-      <c r="G80" s="12" t="inlineStr">
+      <c r="G80" s="12" t="inlineStr"/>
+      <c r="H80" s="12" t="inlineStr"/>
+      <c r="I80" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 신청 대상 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="H80" s="12" t="inlineStr"/>
-      <c r="I80" s="11" t="inlineStr"/>
-      <c r="J80" s="11" t="inlineStr"/>
-      <c r="K80" s="12" t="inlineStr"/>
+      <c r="J80" s="12" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr"/>
+      <c r="L80" s="11" t="inlineStr"/>
+      <c r="M80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -3022,9 +3199,11 @@
       <c r="F81" s="8" t="inlineStr"/>
       <c r="G81" s="8" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="6" t="inlineStr"/>
-      <c r="J81" s="6" t="inlineStr"/>
-      <c r="K81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr"/>
+      <c r="L81" s="6" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -3049,9 +3228,11 @@
       <c r="F82" s="8" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr"/>
       <c r="H82" s="8" t="inlineStr"/>
-      <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="6" t="inlineStr"/>
-      <c r="K82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr"/>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
+      <c r="L82" s="6" t="inlineStr"/>
+      <c r="M82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -3076,9 +3257,11 @@
       <c r="F83" s="8" t="inlineStr"/>
       <c r="G83" s="8" t="inlineStr"/>
       <c r="H83" s="8" t="inlineStr"/>
-      <c r="I83" s="6" t="inlineStr"/>
-      <c r="J83" s="6" t="inlineStr"/>
-      <c r="K83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
+      <c r="L83" s="6" t="inlineStr"/>
+      <c r="M83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -3103,9 +3286,11 @@
       <c r="F84" s="8" t="inlineStr"/>
       <c r="G84" s="8" t="inlineStr"/>
       <c r="H84" s="8" t="inlineStr"/>
-      <c r="I84" s="6" t="inlineStr"/>
-      <c r="J84" s="6" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
+      <c r="L84" s="6" t="inlineStr"/>
+      <c r="M84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -3130,9 +3315,11 @@
       <c r="F85" s="8" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr"/>
       <c r="H85" s="8" t="inlineStr"/>
-      <c r="I85" s="6" t="inlineStr"/>
-      <c r="J85" s="6" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr"/>
+      <c r="J85" s="8" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr"/>
+      <c r="L85" s="6" t="inlineStr"/>
+      <c r="M85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -3157,9 +3344,11 @@
       <c r="F86" s="8" t="inlineStr"/>
       <c r="G86" s="8" t="inlineStr"/>
       <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="6" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr"/>
+      <c r="L86" s="6" t="inlineStr"/>
+      <c r="M86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -3184,9 +3373,11 @@
       <c r="F87" s="8" t="inlineStr"/>
       <c r="G87" s="8" t="inlineStr"/>
       <c r="H87" s="8" t="inlineStr"/>
-      <c r="I87" s="6" t="inlineStr"/>
-      <c r="J87" s="6" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
+      <c r="L87" s="6" t="inlineStr"/>
+      <c r="M87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n">
@@ -3209,15 +3400,17 @@
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr"/>
-      <c r="G88" s="12" t="inlineStr">
+      <c r="G88" s="12" t="inlineStr"/>
+      <c r="H88" s="12" t="inlineStr"/>
+      <c r="I88" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에는 '목양관리'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="H88" s="12" t="inlineStr"/>
-      <c r="I88" s="11" t="inlineStr"/>
-      <c r="J88" s="11" t="inlineStr"/>
-      <c r="K88" s="12" t="inlineStr"/>
+      <c r="J88" s="12" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr"/>
+      <c r="L88" s="11" t="inlineStr"/>
+      <c r="M88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -3240,15 +3433,17 @@
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr"/>
-      <c r="G89" s="12" t="inlineStr">
+      <c r="G89" s="12" t="inlineStr"/>
+      <c r="H89" s="12" t="inlineStr"/>
+      <c r="I89" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에는 '서기'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="H89" s="12" t="inlineStr"/>
-      <c r="I89" s="11" t="inlineStr"/>
-      <c r="J89" s="11" t="inlineStr"/>
-      <c r="K89" s="12" t="inlineStr"/>
+      <c r="J89" s="12" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr"/>
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -3271,15 +3466,17 @@
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr"/>
-      <c r="G90" s="12" t="inlineStr">
+      <c r="G90" s="12" t="inlineStr"/>
+      <c r="H90" s="12" t="inlineStr"/>
+      <c r="I90" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있음 — 임명직인지 확인 필요</t>
         </is>
       </c>
-      <c r="H90" s="12" t="inlineStr"/>
-      <c r="I90" s="11" t="inlineStr"/>
-      <c r="J90" s="11" t="inlineStr"/>
-      <c r="K90" s="12" t="inlineStr"/>
+      <c r="J90" s="12" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr"/>
+      <c r="L90" s="11" t="inlineStr"/>
+      <c r="M90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
@@ -3304,9 +3501,11 @@
       <c r="F91" s="10" t="inlineStr"/>
       <c r="G91" s="10" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr"/>
-      <c r="I91" s="9" t="inlineStr"/>
-      <c r="J91" s="9" t="inlineStr"/>
-      <c r="K91" s="10" t="inlineStr"/>
+      <c r="I91" s="10" t="inlineStr"/>
+      <c r="J91" s="10" t="inlineStr"/>
+      <c r="K91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr"/>
+      <c r="M91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -3331,9 +3530,11 @@
       <c r="F92" s="8" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr"/>
       <c r="H92" s="8" t="inlineStr"/>
-      <c r="I92" s="6" t="inlineStr"/>
-      <c r="J92" s="6" t="inlineStr"/>
-      <c r="K92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
+      <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr"/>
+      <c r="L92" s="6" t="inlineStr"/>
+      <c r="M92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -3358,9 +3559,11 @@
       <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
       <c r="H93" s="8" t="inlineStr"/>
-      <c r="I93" s="6" t="inlineStr"/>
-      <c r="J93" s="6" t="inlineStr"/>
-      <c r="K93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr"/>
+      <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr"/>
+      <c r="M93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -3385,9 +3588,11 @@
       <c r="F94" s="8" t="inlineStr"/>
       <c r="G94" s="8" t="inlineStr"/>
       <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="6" t="inlineStr"/>
-      <c r="J94" s="6" t="inlineStr"/>
-      <c r="K94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr"/>
+      <c r="M94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
@@ -3412,9 +3617,11 @@
       <c r="F95" s="10" t="inlineStr"/>
       <c r="G95" s="10" t="inlineStr"/>
       <c r="H95" s="10" t="inlineStr"/>
-      <c r="I95" s="9" t="inlineStr"/>
-      <c r="J95" s="9" t="inlineStr"/>
-      <c r="K95" s="10" t="inlineStr"/>
+      <c r="I95" s="10" t="inlineStr"/>
+      <c r="J95" s="10" t="inlineStr"/>
+      <c r="K95" s="9" t="inlineStr"/>
+      <c r="L95" s="9" t="inlineStr"/>
+      <c r="M95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -3439,9 +3646,11 @@
       <c r="F96" s="8" t="inlineStr"/>
       <c r="G96" s="8" t="inlineStr"/>
       <c r="H96" s="8" t="inlineStr"/>
-      <c r="I96" s="6" t="inlineStr"/>
-      <c r="J96" s="6" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr"/>
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr"/>
+      <c r="L96" s="6" t="inlineStr"/>
+      <c r="M96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -3466,9 +3675,11 @@
       <c r="F97" s="8" t="inlineStr"/>
       <c r="G97" s="8" t="inlineStr"/>
       <c r="H97" s="8" t="inlineStr"/>
-      <c r="I97" s="6" t="inlineStr"/>
-      <c r="J97" s="6" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr"/>
+      <c r="L97" s="6" t="inlineStr"/>
+      <c r="M97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -3493,9 +3704,11 @@
       <c r="F98" s="8" t="inlineStr"/>
       <c r="G98" s="8" t="inlineStr"/>
       <c r="H98" s="8" t="inlineStr"/>
-      <c r="I98" s="6" t="inlineStr"/>
-      <c r="J98" s="6" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
+      <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr"/>
+      <c r="L98" s="6" t="inlineStr"/>
+      <c r="M98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -3520,14 +3733,16 @@
       <c r="F99" s="8" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr"/>
       <c r="H99" s="8" t="inlineStr"/>
-      <c r="I99" s="6" t="inlineStr"/>
-      <c r="J99" s="6" t="inlineStr"/>
-      <c r="K99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr"/>
+      <c r="M99" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K99"/>
+  <autoFilter ref="A1:M99"/>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
+    <dataValidation sqref="K2:K99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
       <formula1>"유지,이름 수정,신설,폐지"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ministry/2026_사역신청_부서확인양식.xlsx
+++ b/ministry/2026_사역신청_부서확인양식.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="임명직 전용 부서" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$M$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$N$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -572,54 +572,61 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4. J열 '확정 표기명'에 2026년 최종 명칭을 적어 주세요(그대로면 D열과 동일하게 적어도 됩니다).</t>
+          <t>4. H열 '필요 인원'은 채워 주시면 좋지만 선택 사항입니다 — 정원을 세거나 막는 데 쓰지 않고, 성도님께 참고로만 보여드립니다. 모르시면 비워 두셔도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5. K열 '변경여부'는 목록에서 유지 / 이름 수정 / 신설 / 폐지 중 하나를 골라 주세요.</t>
+          <t>5. K열 '확정 표기명'에 2026년 최종 명칭을 적어 주세요(그대로면 D열과 동일하게 적어도 됩니다).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>6. L열에 확인하신 분 성함을, M열에는 그 밖에 전달할 내용을 적어 주세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+          <t>6. L열 '변경여부'는 목록에서 유지 / 이름 수정 / 신설 / 폐지 중 하나를 골라 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>7. M열에 확인하신 분 성함을, N열에는 그 밖에 전달할 내용을 적어 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>색이 칠해진 자리</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>▨ 분홍색 행 — 두 원본 문서(인사표·신청서)의 표기가 서로 달라 어느 쪽이 맞는지 확인이 필요한 자리입니다. I열 '확인이 필요한 사유'에 무엇이 다른지 적어 두었습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>▨ 회색 행 — 신청이 아니라 지명으로 맡는 임명직입니다. 성도가 직접 신청하지 않으므로 앱의 신청 목록에는 넣지 않습니다. 이름이 맞는지만 확인해 주세요(시간·요일은 안 채우셔도 됩니다).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="2" t="inlineStr">
+          <t>▨ 분홍색 행 — 두 원본 문서(인사표·신청서)의 표기가 서로 달라 어느 쪽이 맞는지 확인이 필요한 자리입니다. J열 '확인이 필요한 사유'에 무엇이 다른지 적어 두었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>▨ 회색 행 — 신청이 아니라 지명으로 맡는 임명직입니다. 성도가 직접 신청하지 않으므로 앱의 신청 목록에는 넣지 않습니다. 이름이 맞는지만 확인해 주세요(시간·요일·인원은 안 채우셔도 됩니다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>임명직만 있어 개별 사역팀이 없는 부서(M-12부·재정부·감사위원회 등)는 「임명직 전용 부서」 시트에 따로 안내했습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>문의: 제자양육부 신앙운동팀</t>
         </is>
@@ -636,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -646,12 +653,13 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -692,30 +700,35 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
+          <t>필요 인원 (참고, 선택 기입)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
           <t>하위 선택 안내</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>확인이 필요한 사유</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>확정 표기명 (부서 기입)</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>변경여부</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>담당자 확인 (성명)</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -743,12 +756,13 @@
       </c>
       <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="6" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
       <c r="L2" s="6" t="inlineStr"/>
-      <c r="M2" s="8" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -772,12 +786,13 @@
       </c>
       <c r="F3" s="8" t="inlineStr"/>
       <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="6" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="6" t="inlineStr"/>
-      <c r="M3" s="8" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -801,12 +816,13 @@
       </c>
       <c r="F4" s="8" t="inlineStr"/>
       <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -834,16 +850,17 @@
       </c>
       <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
-      <c r="M5" s="8" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -871,16 +888,17 @@
       </c>
       <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -908,16 +926,17 @@
       </c>
       <c r="F7" s="8" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
-      <c r="M7" s="8" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -945,16 +964,17 @@
       </c>
       <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>어와나 4개 중 하나만 신청</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
       <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="K8" s="8" t="inlineStr"/>
       <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -982,12 +1002,13 @@
       </c>
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="8" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -1015,12 +1036,13 @@
       </c>
       <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="8" t="inlineStr"/>
       <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="6" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1048,12 +1070,13 @@
       </c>
       <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
-      <c r="K11" s="6" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr"/>
-      <c r="M11" s="8" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1081,12 +1104,13 @@
       </c>
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="6" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1114,12 +1138,13 @@
       </c>
       <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr"/>
       <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="8" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -1147,12 +1172,13 @@
       </c>
       <c r="F14" s="8" t="inlineStr"/>
       <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="8" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1180,12 +1206,13 @@
       </c>
       <c r="F15" s="8" t="inlineStr"/>
       <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
       <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="8" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -1213,12 +1240,13 @@
       </c>
       <c r="F16" s="8" t="inlineStr"/>
       <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="6" t="inlineStr"/>
+      <c r="K16" s="8" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="8" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1246,12 +1274,13 @@
       </c>
       <c r="F17" s="8" t="inlineStr"/>
       <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
-      <c r="K17" s="6" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
-      <c r="M17" s="8" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -1279,12 +1308,13 @@
       </c>
       <c r="F18" s="8" t="inlineStr"/>
       <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="8" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1312,12 +1342,13 @@
       </c>
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
       <c r="L19" s="6" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1341,12 +1372,13 @@
       </c>
       <c r="F20" s="10" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
       <c r="I20" s="10" t="inlineStr"/>
       <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1370,12 +1402,13 @@
       </c>
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -1399,12 +1432,13 @@
       </c>
       <c r="F22" s="8" t="inlineStr"/>
       <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="8" t="inlineStr"/>
       <c r="J22" s="8" t="inlineStr"/>
-      <c r="K22" s="6" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr"/>
       <c r="L22" s="6" t="inlineStr"/>
-      <c r="M22" s="8" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1428,12 +1462,13 @@
       </c>
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" s="8" t="inlineStr"/>
       <c r="J23" s="8" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
-      <c r="M23" s="8" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -1457,12 +1492,13 @@
       </c>
       <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="8" t="inlineStr"/>
-      <c r="K24" s="6" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
-      <c r="M24" s="8" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1486,16 +1522,17 @@
       </c>
       <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>다른 찬양대와 겸직 가능한 유일한 예외</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr"/>
       <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
-      <c r="M25" s="8" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -1519,12 +1556,13 @@
       </c>
       <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="8" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
-      <c r="M26" s="8" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1548,12 +1586,13 @@
       </c>
       <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="8" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
       <c r="L27" s="6" t="inlineStr"/>
-      <c r="M27" s="8" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -1577,12 +1616,13 @@
       </c>
       <c r="F28" s="8" t="inlineStr"/>
       <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" s="8" t="inlineStr"/>
       <c r="J28" s="8" t="inlineStr"/>
-      <c r="K28" s="6" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr"/>
-      <c r="M28" s="8" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1606,12 +1646,13 @@
       </c>
       <c r="F29" s="8" t="inlineStr"/>
       <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="8" t="inlineStr"/>
-      <c r="K29" s="6" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
       <c r="L29" s="6" t="inlineStr"/>
-      <c r="M29" s="8" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -1635,12 +1676,13 @@
       </c>
       <c r="F30" s="8" t="inlineStr"/>
       <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="8" t="inlineStr"/>
-      <c r="K30" s="6" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr"/>
       <c r="L30" s="6" t="inlineStr"/>
-      <c r="M30" s="8" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1664,12 +1706,13 @@
       </c>
       <c r="F31" s="8" t="inlineStr"/>
       <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="8" t="inlineStr"/>
       <c r="J31" s="8" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
       <c r="L31" s="6" t="inlineStr"/>
-      <c r="M31" s="8" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -1693,12 +1736,13 @@
       </c>
       <c r="F32" s="8" t="inlineStr"/>
       <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr"/>
       <c r="J32" s="8" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="K32" s="8" t="inlineStr"/>
       <c r="L32" s="6" t="inlineStr"/>
-      <c r="M32" s="8" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr"/>
+      <c r="N32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1722,12 +1766,13 @@
       </c>
       <c r="F33" s="8" t="inlineStr"/>
       <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr"/>
       <c r="L33" s="6" t="inlineStr"/>
-      <c r="M33" s="8" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -1751,12 +1796,13 @@
       </c>
       <c r="F34" s="8" t="inlineStr"/>
       <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" s="8" t="inlineStr"/>
       <c r="J34" s="8" t="inlineStr"/>
-      <c r="K34" s="6" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr"/>
-      <c r="M34" s="8" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1780,12 +1826,13 @@
       </c>
       <c r="F35" s="8" t="inlineStr"/>
       <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="6" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
       <c r="L35" s="6" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -1809,12 +1856,13 @@
       </c>
       <c r="F36" s="8" t="inlineStr"/>
       <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="8" t="inlineStr"/>
       <c r="J36" s="8" t="inlineStr"/>
-      <c r="K36" s="6" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr"/>
       <c r="L36" s="6" t="inlineStr"/>
-      <c r="M36" s="8" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -1838,12 +1886,13 @@
       </c>
       <c r="F37" s="8" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="6" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
       <c r="L37" s="6" t="inlineStr"/>
-      <c r="M37" s="8" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -1867,12 +1916,13 @@
       </c>
       <c r="F38" s="8" t="inlineStr"/>
       <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" s="8" t="inlineStr"/>
       <c r="J38" s="8" t="inlineStr"/>
-      <c r="K38" s="6" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr"/>
       <c r="L38" s="6" t="inlineStr"/>
-      <c r="M38" s="8" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr"/>
+      <c r="N38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -1896,12 +1946,13 @@
       </c>
       <c r="F39" s="8" t="inlineStr"/>
       <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" s="8" t="inlineStr"/>
       <c r="J39" s="8" t="inlineStr"/>
-      <c r="K39" s="6" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr"/>
       <c r="L39" s="6" t="inlineStr"/>
-      <c r="M39" s="8" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -1925,12 +1976,13 @@
       </c>
       <c r="F40" s="8" t="inlineStr"/>
       <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="8" t="inlineStr"/>
       <c r="J40" s="8" t="inlineStr"/>
-      <c r="K40" s="6" t="inlineStr"/>
+      <c r="K40" s="8" t="inlineStr"/>
       <c r="L40" s="6" t="inlineStr"/>
-      <c r="M40" s="8" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr"/>
+      <c r="N40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -1954,12 +2006,13 @@
       </c>
       <c r="F41" s="8" t="inlineStr"/>
       <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="8" t="inlineStr"/>
-      <c r="K41" s="6" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
       <c r="L41" s="6" t="inlineStr"/>
-      <c r="M41" s="8" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -1983,12 +2036,13 @@
       </c>
       <c r="F42" s="8" t="inlineStr"/>
       <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="8" t="inlineStr"/>
       <c r="J42" s="8" t="inlineStr"/>
-      <c r="K42" s="6" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr"/>
       <c r="L42" s="6" t="inlineStr"/>
-      <c r="M42" s="8" t="inlineStr"/>
+      <c r="M42" s="6" t="inlineStr"/>
+      <c r="N42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -2012,12 +2066,13 @@
       </c>
       <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr"/>
-      <c r="K43" s="6" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="6" t="inlineStr"/>
-      <c r="M43" s="8" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -2041,12 +2096,13 @@
       </c>
       <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="8" t="inlineStr"/>
       <c r="J44" s="8" t="inlineStr"/>
-      <c r="K44" s="6" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="6" t="inlineStr"/>
-      <c r="M44" s="8" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
+      <c r="N44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -2070,12 +2126,13 @@
       </c>
       <c r="F45" s="8" t="inlineStr"/>
       <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="8" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="8" t="inlineStr"/>
       <c r="J45" s="8" t="inlineStr"/>
-      <c r="K45" s="6" t="inlineStr"/>
+      <c r="K45" s="8" t="inlineStr"/>
       <c r="L45" s="6" t="inlineStr"/>
-      <c r="M45" s="8" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -2099,12 +2156,13 @@
       </c>
       <c r="F46" s="8" t="inlineStr"/>
       <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="8" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="8" t="inlineStr"/>
       <c r="J46" s="8" t="inlineStr"/>
-      <c r="K46" s="6" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr"/>
       <c r="L46" s="6" t="inlineStr"/>
-      <c r="M46" s="8" t="inlineStr"/>
+      <c r="M46" s="6" t="inlineStr"/>
+      <c r="N46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -2128,12 +2186,13 @@
       </c>
       <c r="F47" s="8" t="inlineStr"/>
       <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="8" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="8" t="inlineStr"/>
       <c r="J47" s="8" t="inlineStr"/>
-      <c r="K47" s="6" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
       <c r="L47" s="6" t="inlineStr"/>
-      <c r="M47" s="8" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="n">
@@ -2157,12 +2216,13 @@
       </c>
       <c r="F48" s="10" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr"/>
-      <c r="H48" s="10" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
       <c r="I48" s="10" t="inlineStr"/>
       <c r="J48" s="10" t="inlineStr"/>
-      <c r="K48" s="9" t="inlineStr"/>
+      <c r="K48" s="10" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
+      <c r="M48" s="9" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
@@ -2186,16 +2246,17 @@
       </c>
       <c r="F49" s="12" t="inlineStr"/>
       <c r="G49" s="12" t="inlineStr"/>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr"/>
+      <c r="I49" s="12" t="inlineStr"/>
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>조직표에는 회계(최현희)가 있으나 신청서 양식에는 없음 — 임명직인지, 신청서 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="J49" s="12" t="inlineStr"/>
-      <c r="K49" s="11" t="inlineStr"/>
+      <c r="K49" s="12" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr"/>
-      <c r="M49" s="12" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr"/>
+      <c r="N49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -2219,12 +2280,13 @@
       </c>
       <c r="F50" s="8" t="inlineStr"/>
       <c r="G50" s="8" t="inlineStr"/>
-      <c r="H50" s="8" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="8" t="inlineStr"/>
       <c r="J50" s="8" t="inlineStr"/>
-      <c r="K50" s="6" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr"/>
       <c r="L50" s="6" t="inlineStr"/>
-      <c r="M50" s="8" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -2248,12 +2310,13 @@
       </c>
       <c r="F51" s="8" t="inlineStr"/>
       <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="8" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="8" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr"/>
-      <c r="K51" s="6" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr"/>
       <c r="L51" s="6" t="inlineStr"/>
-      <c r="M51" s="8" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -2277,12 +2340,13 @@
       </c>
       <c r="F52" s="8" t="inlineStr"/>
       <c r="G52" s="8" t="inlineStr"/>
-      <c r="H52" s="8" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="8" t="inlineStr"/>
       <c r="J52" s="8" t="inlineStr"/>
-      <c r="K52" s="6" t="inlineStr"/>
+      <c r="K52" s="8" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
-      <c r="M52" s="8" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -2306,12 +2370,13 @@
       </c>
       <c r="F53" s="8" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr"/>
-      <c r="H53" s="8" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
-      <c r="K53" s="6" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr"/>
       <c r="L53" s="6" t="inlineStr"/>
-      <c r="M53" s="8" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -2335,12 +2400,13 @@
       </c>
       <c r="F54" s="8" t="inlineStr"/>
       <c r="G54" s="8" t="inlineStr"/>
-      <c r="H54" s="8" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="8" t="inlineStr"/>
       <c r="J54" s="8" t="inlineStr"/>
-      <c r="K54" s="6" t="inlineStr"/>
+      <c r="K54" s="8" t="inlineStr"/>
       <c r="L54" s="6" t="inlineStr"/>
-      <c r="M54" s="8" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2364,12 +2430,13 @@
       </c>
       <c r="F55" s="8" t="inlineStr"/>
       <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="8" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="8" t="inlineStr"/>
       <c r="J55" s="8" t="inlineStr"/>
-      <c r="K55" s="6" t="inlineStr"/>
+      <c r="K55" s="8" t="inlineStr"/>
       <c r="L55" s="6" t="inlineStr"/>
-      <c r="M55" s="8" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -2397,16 +2464,17 @@
       </c>
       <c r="F56" s="8" t="inlineStr"/>
       <c r="G56" s="8" t="inlineStr"/>
-      <c r="H56" s="8" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr"/>
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>행복전도대 요일 중 하나 이상 신청</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr"/>
       <c r="J56" s="8" t="inlineStr"/>
-      <c r="K56" s="6" t="inlineStr"/>
+      <c r="K56" s="8" t="inlineStr"/>
       <c r="L56" s="6" t="inlineStr"/>
-      <c r="M56" s="8" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2434,16 +2502,17 @@
       </c>
       <c r="F57" s="8" t="inlineStr"/>
       <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>행복전도대 요일 중 하나 이상 신청</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr"/>
       <c r="J57" s="8" t="inlineStr"/>
-      <c r="K57" s="6" t="inlineStr"/>
+      <c r="K57" s="8" t="inlineStr"/>
       <c r="L57" s="6" t="inlineStr"/>
-      <c r="M57" s="8" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -2467,12 +2536,13 @@
       </c>
       <c r="F58" s="8" t="inlineStr"/>
       <c r="G58" s="8" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="8" t="inlineStr"/>
       <c r="J58" s="8" t="inlineStr"/>
-      <c r="K58" s="6" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr"/>
       <c r="L58" s="6" t="inlineStr"/>
-      <c r="M58" s="8" t="inlineStr"/>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2496,12 +2566,13 @@
       </c>
       <c r="F59" s="8" t="inlineStr"/>
       <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="8" t="inlineStr"/>
       <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="6" t="inlineStr"/>
+      <c r="K59" s="8" t="inlineStr"/>
       <c r="L59" s="6" t="inlineStr"/>
-      <c r="M59" s="8" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
@@ -2525,12 +2596,13 @@
       </c>
       <c r="F60" s="8" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr"/>
-      <c r="H60" s="8" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="8" t="inlineStr"/>
       <c r="J60" s="8" t="inlineStr"/>
-      <c r="K60" s="6" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="6" t="inlineStr"/>
-      <c r="M60" s="8" t="inlineStr"/>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -2554,12 +2626,13 @@
       </c>
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="8" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="8" t="inlineStr"/>
       <c r="J61" s="8" t="inlineStr"/>
-      <c r="K61" s="6" t="inlineStr"/>
+      <c r="K61" s="8" t="inlineStr"/>
       <c r="L61" s="6" t="inlineStr"/>
-      <c r="M61" s="8" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
@@ -2583,12 +2656,13 @@
       </c>
       <c r="F62" s="8" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="8" t="inlineStr"/>
       <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="6" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
-      <c r="M62" s="8" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -2612,12 +2686,13 @@
       </c>
       <c r="F63" s="8" t="inlineStr"/>
       <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="8" t="inlineStr"/>
       <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="6" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
-      <c r="M63" s="8" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
@@ -2641,12 +2716,13 @@
       </c>
       <c r="F64" s="8" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="8" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="8" t="inlineStr"/>
       <c r="J64" s="8" t="inlineStr"/>
-      <c r="K64" s="6" t="inlineStr"/>
+      <c r="K64" s="8" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
-      <c r="M64" s="8" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -2670,12 +2746,13 @@
       </c>
       <c r="F65" s="8" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" s="8" t="inlineStr"/>
       <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="6" t="inlineStr"/>
+      <c r="K65" s="8" t="inlineStr"/>
       <c r="L65" s="6" t="inlineStr"/>
-      <c r="M65" s="8" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
@@ -2699,12 +2776,13 @@
       </c>
       <c r="F66" s="8" t="inlineStr"/>
       <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="8" t="inlineStr"/>
       <c r="J66" s="8" t="inlineStr"/>
-      <c r="K66" s="6" t="inlineStr"/>
+      <c r="K66" s="8" t="inlineStr"/>
       <c r="L66" s="6" t="inlineStr"/>
-      <c r="M66" s="8" t="inlineStr"/>
+      <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -2728,12 +2806,13 @@
       </c>
       <c r="F67" s="8" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="8" t="inlineStr"/>
       <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="6" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr"/>
       <c r="L67" s="6" t="inlineStr"/>
-      <c r="M67" s="8" t="inlineStr"/>
+      <c r="M67" s="6" t="inlineStr"/>
+      <c r="N67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n">
@@ -2757,16 +2836,17 @@
       </c>
       <c r="F68" s="12" t="inlineStr"/>
       <c r="G68" s="12" t="inlineStr"/>
-      <c r="H68" s="12" t="inlineStr"/>
-      <c r="I68" s="12" t="inlineStr">
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="12" t="inlineStr"/>
+      <c r="J68" s="12" t="inlineStr">
         <is>
           <t>신청서에만 있고 조직표(인사표)에는 없음 — 신설 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="J68" s="12" t="inlineStr"/>
-      <c r="K68" s="11" t="inlineStr"/>
+      <c r="K68" s="12" t="inlineStr"/>
       <c r="L68" s="11" t="inlineStr"/>
-      <c r="M68" s="12" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr"/>
+      <c r="N68" s="12" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
@@ -2790,16 +2870,17 @@
       </c>
       <c r="F69" s="12" t="inlineStr"/>
       <c r="G69" s="12" t="inlineStr"/>
-      <c r="H69" s="12" t="inlineStr"/>
-      <c r="I69" s="12" t="inlineStr">
+      <c r="H69" s="11" t="inlineStr"/>
+      <c r="I69" s="12" t="inlineStr"/>
+      <c r="J69" s="12" t="inlineStr">
         <is>
           <t>신청서에만 있고 조직표(인사표)에는 없음 — 신설 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="J69" s="12" t="inlineStr"/>
-      <c r="K69" s="11" t="inlineStr"/>
+      <c r="K69" s="12" t="inlineStr"/>
       <c r="L69" s="11" t="inlineStr"/>
-      <c r="M69" s="12" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr"/>
+      <c r="N69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -2827,16 +2908,17 @@
       </c>
       <c r="F70" s="8" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>주일찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr"/>
       <c r="J70" s="8" t="inlineStr"/>
-      <c r="K70" s="6" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
-      <c r="M70" s="8" t="inlineStr"/>
+      <c r="M70" s="6" t="inlineStr"/>
+      <c r="N70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -2864,16 +2946,17 @@
       </c>
       <c r="F71" s="8" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>주일찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr"/>
       <c r="J71" s="8" t="inlineStr"/>
-      <c r="K71" s="6" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
-      <c r="M71" s="8" t="inlineStr"/>
+      <c r="M71" s="6" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
@@ -2901,16 +2984,17 @@
       </c>
       <c r="F72" s="8" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H72" s="6" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>주일찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr"/>
       <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="6" t="inlineStr"/>
+      <c r="K72" s="8" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
-      <c r="M72" s="8" t="inlineStr"/>
+      <c r="M72" s="6" t="inlineStr"/>
+      <c r="N72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -2938,16 +3022,17 @@
       </c>
       <c r="F73" s="8" t="inlineStr"/>
       <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>수요찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr"/>
       <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="6" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
-      <c r="M73" s="8" t="inlineStr"/>
+      <c r="M73" s="6" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
@@ -2975,16 +3060,17 @@
       </c>
       <c r="F74" s="8" t="inlineStr"/>
       <c r="G74" s="8" t="inlineStr"/>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>수요찬양 봉사 시간대 중 택1</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr"/>
       <c r="J74" s="8" t="inlineStr"/>
-      <c r="K74" s="6" t="inlineStr"/>
+      <c r="K74" s="8" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
-      <c r="M74" s="8" t="inlineStr"/>
+      <c r="M74" s="6" t="inlineStr"/>
+      <c r="N74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -3008,12 +3094,13 @@
       </c>
       <c r="F75" s="8" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="8" t="inlineStr"/>
       <c r="J75" s="8" t="inlineStr"/>
-      <c r="K75" s="6" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
-      <c r="M75" s="8" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr"/>
+      <c r="N75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n">
@@ -3037,12 +3124,13 @@
       </c>
       <c r="F76" s="8" t="inlineStr"/>
       <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="8" t="inlineStr"/>
       <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="6" t="inlineStr"/>
+      <c r="K76" s="8" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
-      <c r="M76" s="8" t="inlineStr"/>
+      <c r="M76" s="6" t="inlineStr"/>
+      <c r="N76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n">
@@ -3066,16 +3154,17 @@
       </c>
       <c r="F77" s="12" t="inlineStr"/>
       <c r="G77" s="12" t="inlineStr"/>
-      <c r="H77" s="12" t="inlineStr"/>
-      <c r="I77" s="12" t="inlineStr">
+      <c r="H77" s="11" t="inlineStr"/>
+      <c r="I77" s="12" t="inlineStr"/>
+      <c r="J77" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 임명직으로 볼지 확인 필요</t>
         </is>
       </c>
-      <c r="J77" s="12" t="inlineStr"/>
-      <c r="K77" s="11" t="inlineStr"/>
+      <c r="K77" s="12" t="inlineStr"/>
       <c r="L77" s="11" t="inlineStr"/>
-      <c r="M77" s="12" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
+      <c r="N77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n">
@@ -3099,16 +3188,17 @@
       </c>
       <c r="F78" s="12" t="inlineStr"/>
       <c r="G78" s="12" t="inlineStr"/>
-      <c r="H78" s="12" t="inlineStr"/>
-      <c r="I78" s="12" t="inlineStr">
+      <c r="H78" s="11" t="inlineStr"/>
+      <c r="I78" s="12" t="inlineStr"/>
+      <c r="J78" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 임명직으로 볼지 확인 필요</t>
         </is>
       </c>
-      <c r="J78" s="12" t="inlineStr"/>
-      <c r="K78" s="11" t="inlineStr"/>
+      <c r="K78" s="12" t="inlineStr"/>
       <c r="L78" s="11" t="inlineStr"/>
-      <c r="M78" s="12" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr"/>
+      <c r="N78" s="12" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n">
@@ -3132,16 +3222,17 @@
       </c>
       <c r="F79" s="12" t="inlineStr"/>
       <c r="G79" s="12" t="inlineStr"/>
-      <c r="H79" s="12" t="inlineStr"/>
-      <c r="I79" s="12" t="inlineStr">
+      <c r="H79" s="11" t="inlineStr"/>
+      <c r="I79" s="12" t="inlineStr"/>
+      <c r="J79" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 신청 대상 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="J79" s="12" t="inlineStr"/>
-      <c r="K79" s="11" t="inlineStr"/>
+      <c r="K79" s="12" t="inlineStr"/>
       <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="12" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr"/>
+      <c r="N79" s="12" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n">
@@ -3165,16 +3256,17 @@
       </c>
       <c r="F80" s="12" t="inlineStr"/>
       <c r="G80" s="12" t="inlineStr"/>
-      <c r="H80" s="12" t="inlineStr"/>
-      <c r="I80" s="12" t="inlineStr">
+      <c r="H80" s="11" t="inlineStr"/>
+      <c r="I80" s="12" t="inlineStr"/>
+      <c r="J80" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 신청 대상 누락인지 확인 필요</t>
         </is>
       </c>
-      <c r="J80" s="12" t="inlineStr"/>
-      <c r="K80" s="11" t="inlineStr"/>
+      <c r="K80" s="12" t="inlineStr"/>
       <c r="L80" s="11" t="inlineStr"/>
-      <c r="M80" s="12" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr"/>
+      <c r="N80" s="12" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -3198,12 +3290,13 @@
       </c>
       <c r="F81" s="8" t="inlineStr"/>
       <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="8" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr"/>
       <c r="J81" s="8" t="inlineStr"/>
-      <c r="K81" s="6" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
       <c r="L81" s="6" t="inlineStr"/>
-      <c r="M81" s="8" t="inlineStr"/>
+      <c r="M81" s="6" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n">
@@ -3227,12 +3320,13 @@
       </c>
       <c r="F82" s="8" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr"/>
-      <c r="H82" s="8" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" s="8" t="inlineStr"/>
       <c r="J82" s="8" t="inlineStr"/>
-      <c r="K82" s="6" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
       <c r="L82" s="6" t="inlineStr"/>
-      <c r="M82" s="8" t="inlineStr"/>
+      <c r="M82" s="6" t="inlineStr"/>
+      <c r="N82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -3256,12 +3350,13 @@
       </c>
       <c r="F83" s="8" t="inlineStr"/>
       <c r="G83" s="8" t="inlineStr"/>
-      <c r="H83" s="8" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" s="8" t="inlineStr"/>
       <c r="J83" s="8" t="inlineStr"/>
-      <c r="K83" s="6" t="inlineStr"/>
+      <c r="K83" s="8" t="inlineStr"/>
       <c r="L83" s="6" t="inlineStr"/>
-      <c r="M83" s="8" t="inlineStr"/>
+      <c r="M83" s="6" t="inlineStr"/>
+      <c r="N83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n">
@@ -3285,12 +3380,13 @@
       </c>
       <c r="F84" s="8" t="inlineStr"/>
       <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="8" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="8" t="inlineStr"/>
       <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="6" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
       <c r="L84" s="6" t="inlineStr"/>
-      <c r="M84" s="8" t="inlineStr"/>
+      <c r="M84" s="6" t="inlineStr"/>
+      <c r="N84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -3314,12 +3410,13 @@
       </c>
       <c r="F85" s="8" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="8" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="6" t="inlineStr"/>
+      <c r="K85" s="8" t="inlineStr"/>
       <c r="L85" s="6" t="inlineStr"/>
-      <c r="M85" s="8" t="inlineStr"/>
+      <c r="M85" s="6" t="inlineStr"/>
+      <c r="N85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n">
@@ -3343,12 +3440,13 @@
       </c>
       <c r="F86" s="8" t="inlineStr"/>
       <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" s="8" t="inlineStr"/>
       <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="6" t="inlineStr"/>
+      <c r="K86" s="8" t="inlineStr"/>
       <c r="L86" s="6" t="inlineStr"/>
-      <c r="M86" s="8" t="inlineStr"/>
+      <c r="M86" s="6" t="inlineStr"/>
+      <c r="N86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -3372,12 +3470,13 @@
       </c>
       <c r="F87" s="8" t="inlineStr"/>
       <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" s="8" t="inlineStr"/>
       <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="6" t="inlineStr"/>
+      <c r="K87" s="8" t="inlineStr"/>
       <c r="L87" s="6" t="inlineStr"/>
-      <c r="M87" s="8" t="inlineStr"/>
+      <c r="M87" s="6" t="inlineStr"/>
+      <c r="N87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n">
@@ -3401,16 +3500,17 @@
       </c>
       <c r="F88" s="12" t="inlineStr"/>
       <c r="G88" s="12" t="inlineStr"/>
-      <c r="H88" s="12" t="inlineStr"/>
-      <c r="I88" s="12" t="inlineStr">
+      <c r="H88" s="11" t="inlineStr"/>
+      <c r="I88" s="12" t="inlineStr"/>
+      <c r="J88" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에는 '목양관리'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="J88" s="12" t="inlineStr"/>
-      <c r="K88" s="11" t="inlineStr"/>
+      <c r="K88" s="12" t="inlineStr"/>
       <c r="L88" s="11" t="inlineStr"/>
-      <c r="M88" s="12" t="inlineStr"/>
+      <c r="M88" s="11" t="inlineStr"/>
+      <c r="N88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n">
@@ -3434,16 +3534,17 @@
       </c>
       <c r="F89" s="12" t="inlineStr"/>
       <c r="G89" s="12" t="inlineStr"/>
-      <c r="H89" s="12" t="inlineStr"/>
-      <c r="I89" s="12" t="inlineStr">
+      <c r="H89" s="11" t="inlineStr"/>
+      <c r="I89" s="12" t="inlineStr"/>
+      <c r="J89" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에는 '서기'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
         </is>
       </c>
-      <c r="J89" s="12" t="inlineStr"/>
-      <c r="K89" s="11" t="inlineStr"/>
+      <c r="K89" s="12" t="inlineStr"/>
       <c r="L89" s="11" t="inlineStr"/>
-      <c r="M89" s="12" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr"/>
+      <c r="N89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n">
@@ -3467,16 +3568,17 @@
       </c>
       <c r="F90" s="12" t="inlineStr"/>
       <c r="G90" s="12" t="inlineStr"/>
-      <c r="H90" s="12" t="inlineStr"/>
-      <c r="I90" s="12" t="inlineStr">
+      <c r="H90" s="11" t="inlineStr"/>
+      <c r="I90" s="12" t="inlineStr"/>
+      <c r="J90" s="12" t="inlineStr">
         <is>
           <t>조직표(인사표)에만 있음 — 임명직인지 확인 필요</t>
         </is>
       </c>
-      <c r="J90" s="12" t="inlineStr"/>
-      <c r="K90" s="11" t="inlineStr"/>
+      <c r="K90" s="12" t="inlineStr"/>
       <c r="L90" s="11" t="inlineStr"/>
-      <c r="M90" s="12" t="inlineStr"/>
+      <c r="M90" s="11" t="inlineStr"/>
+      <c r="N90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
@@ -3500,12 +3602,13 @@
       </c>
       <c r="F91" s="10" t="inlineStr"/>
       <c r="G91" s="10" t="inlineStr"/>
-      <c r="H91" s="10" t="inlineStr"/>
+      <c r="H91" s="9" t="inlineStr"/>
       <c r="I91" s="10" t="inlineStr"/>
       <c r="J91" s="10" t="inlineStr"/>
-      <c r="K91" s="9" t="inlineStr"/>
+      <c r="K91" s="10" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr"/>
-      <c r="M91" s="10" t="inlineStr"/>
+      <c r="M91" s="9" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n">
@@ -3529,12 +3632,13 @@
       </c>
       <c r="F92" s="8" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" s="8" t="inlineStr"/>
       <c r="J92" s="8" t="inlineStr"/>
-      <c r="K92" s="6" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
       <c r="L92" s="6" t="inlineStr"/>
-      <c r="M92" s="8" t="inlineStr"/>
+      <c r="M92" s="6" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -3558,12 +3662,13 @@
       </c>
       <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr"/>
       <c r="J93" s="8" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr"/>
       <c r="L93" s="6" t="inlineStr"/>
-      <c r="M93" s="8" t="inlineStr"/>
+      <c r="M93" s="6" t="inlineStr"/>
+      <c r="N93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n">
@@ -3587,12 +3692,13 @@
       </c>
       <c r="F94" s="8" t="inlineStr"/>
       <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="8" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" s="8" t="inlineStr"/>
       <c r="J94" s="8" t="inlineStr"/>
-      <c r="K94" s="6" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr"/>
       <c r="L94" s="6" t="inlineStr"/>
-      <c r="M94" s="8" t="inlineStr"/>
+      <c r="M94" s="6" t="inlineStr"/>
+      <c r="N94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="9" t="n">
@@ -3616,12 +3722,13 @@
       </c>
       <c r="F95" s="10" t="inlineStr"/>
       <c r="G95" s="10" t="inlineStr"/>
-      <c r="H95" s="10" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
       <c r="I95" s="10" t="inlineStr"/>
       <c r="J95" s="10" t="inlineStr"/>
-      <c r="K95" s="9" t="inlineStr"/>
+      <c r="K95" s="10" t="inlineStr"/>
       <c r="L95" s="9" t="inlineStr"/>
-      <c r="M95" s="10" t="inlineStr"/>
+      <c r="M95" s="9" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n">
@@ -3645,12 +3752,13 @@
       </c>
       <c r="F96" s="8" t="inlineStr"/>
       <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="8" t="inlineStr"/>
-      <c r="K96" s="6" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
       <c r="L96" s="6" t="inlineStr"/>
-      <c r="M96" s="8" t="inlineStr"/>
+      <c r="M96" s="6" t="inlineStr"/>
+      <c r="N96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -3674,12 +3782,13 @@
       </c>
       <c r="F97" s="8" t="inlineStr"/>
       <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="inlineStr"/>
+      <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr"/>
       <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="6" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
       <c r="L97" s="6" t="inlineStr"/>
-      <c r="M97" s="8" t="inlineStr"/>
+      <c r="M97" s="6" t="inlineStr"/>
+      <c r="N97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n">
@@ -3703,12 +3812,13 @@
       </c>
       <c r="F98" s="8" t="inlineStr"/>
       <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="8" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="6" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
       <c r="L98" s="6" t="inlineStr"/>
-      <c r="M98" s="8" t="inlineStr"/>
+      <c r="M98" s="6" t="inlineStr"/>
+      <c r="N98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -3732,17 +3842,18 @@
       </c>
       <c r="F99" s="8" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="8" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr"/>
       <c r="J99" s="8" t="inlineStr"/>
-      <c r="K99" s="6" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr"/>
       <c r="L99" s="6" t="inlineStr"/>
-      <c r="M99" s="8" t="inlineStr"/>
+      <c r="M99" s="6" t="inlineStr"/>
+      <c r="N99" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M99"/>
+  <autoFilter ref="A1:N99"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
+    <dataValidation sqref="L2:L99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
       <formula1>"유지,이름 수정,신설,폐지"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ministry/2026_사역신청_부서확인양식.xlsx
+++ b/ministry/2026_사역신청_부서확인양식.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="임명직 전용 부서" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$N$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'사역팀 확인'!$A$1:$N$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,7 +565,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3. F열 '사역 시간·요일'과 G열 '하는 일'을 채워 주세요 — 이 둘은 모든 행이 비어 있습니다(2026-09-07 추가). 성도가 앱에서 사역을 고를 때 이름만 보고는 판단할 수 없어(예: 오병이어 1팀·2팀이 무엇이 다른지) 이번에 함께 걷습니다. 짧게만 적어 주셔도 됩니다(예: '매주 화 오전 10시', '주일 예배 전 주차 안내').</t>
+          <t>3. F열 '사역 시간·요일'과 G열 '하는 일'을 채워 주세요 — 대부분 비어 있습니다(2026-09-07 추가, 찬양부 일부만 먼저 확인되어 채워져 있습니다). 성도가 앱에서 사역을 고를 때 이름만 보고는 판단할 수 없어(예: 오병이어 1팀·2팀이 무엇이 다른지) 이번에 함께 걷습니다. 짧게만 적어 주셔도 됩니다(예: '매주 화 오전 10시', '주일 예배 전 주차 안내').</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N99"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1523,11 +1523,7 @@
       <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>다른 찬양대와 겸직 가능한 유일한 예외</t>
-        </is>
-      </c>
+      <c r="I25" s="8" t="inlineStr"/>
       <c r="J25" s="8" t="inlineStr"/>
       <c r="K25" s="8" t="inlineStr"/>
       <c r="L25" s="6" t="inlineStr"/>
@@ -2447,14 +2443,10 @@
           <t>전도부</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>행복전도대</t>
-        </is>
-      </c>
+      <c r="C56" s="6" t="inlineStr"/>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>금요일</t>
+          <t>행복전도대 - 금요일</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2465,11 +2457,7 @@
       <c r="F56" s="8" t="inlineStr"/>
       <c r="G56" s="8" t="inlineStr"/>
       <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>행복전도대 요일 중 하나 이상 신청</t>
-        </is>
-      </c>
+      <c r="I56" s="8" t="inlineStr"/>
       <c r="J56" s="8" t="inlineStr"/>
       <c r="K56" s="8" t="inlineStr"/>
       <c r="L56" s="6" t="inlineStr"/>
@@ -2485,14 +2473,10 @@
           <t>전도부</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>행복전도대</t>
-        </is>
-      </c>
+      <c r="C57" s="6" t="inlineStr"/>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>토요일</t>
+          <t>행복전도대 - 토요일</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2503,11 +2487,7 @@
       <c r="F57" s="8" t="inlineStr"/>
       <c r="G57" s="8" t="inlineStr"/>
       <c r="H57" s="6" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>행복전도대 요일 중 하나 이상 신청</t>
-        </is>
-      </c>
+      <c r="I57" s="8" t="inlineStr"/>
       <c r="J57" s="8" t="inlineStr"/>
       <c r="K57" s="8" t="inlineStr"/>
       <c r="L57" s="6" t="inlineStr"/>
@@ -2673,7 +2653,11 @@
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr"/>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
           <t>할렐루야찬양대</t>
@@ -2684,7 +2668,11 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>1부</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="8" t="inlineStr"/>
@@ -2703,7 +2691,11 @@
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr"/>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
           <t>임마누엘찬양대</t>
@@ -2714,7 +2706,11 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>2부</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="8" t="inlineStr"/>
@@ -2733,7 +2729,11 @@
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr"/>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
           <t>시온찬양대</t>
@@ -2744,7 +2744,11 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>3부</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" s="8" t="inlineStr"/>
@@ -2763,7 +2767,11 @@
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr"/>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
           <t>실로암찬양대</t>
@@ -2774,7 +2782,11 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>청년</t>
+        </is>
+      </c>
       <c r="G66" s="8" t="inlineStr"/>
       <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="8" t="inlineStr"/>
@@ -2793,7 +2805,11 @@
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr"/>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
           <t>가브리엘찬양대</t>
@@ -2804,7 +2820,11 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>오후</t>
+        </is>
+      </c>
       <c r="G67" s="8" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="8" t="inlineStr"/>
@@ -2815,72 +2835,72 @@
       <c r="N67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="n">
+      <c r="A68" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr"/>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>비파와수금</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="inlineStr"/>
-      <c r="G68" s="12" t="inlineStr"/>
-      <c r="H68" s="11" t="inlineStr"/>
-      <c r="I68" s="12" t="inlineStr"/>
-      <c r="J68" s="12" t="inlineStr">
-        <is>
-          <t>신청서에만 있고 조직표(인사표)에는 없음 — 신설 팀인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K68" s="12" t="inlineStr"/>
-      <c r="L68" s="11" t="inlineStr"/>
-      <c r="M68" s="11" t="inlineStr"/>
-      <c r="N68" s="12" t="inlineStr"/>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>2부 찬양대</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr"/>
+      <c r="J68" s="8" t="inlineStr"/>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="6" t="inlineStr"/>
+      <c r="M68" s="6" t="inlineStr"/>
+      <c r="N68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr"/>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>베데스다</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="inlineStr"/>
-      <c r="G69" s="12" t="inlineStr"/>
-      <c r="H69" s="11" t="inlineStr"/>
-      <c r="I69" s="12" t="inlineStr"/>
-      <c r="J69" s="12" t="inlineStr">
-        <is>
-          <t>신청서에만 있고 조직표(인사표)에는 없음 — 신설 팀인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K69" s="12" t="inlineStr"/>
-      <c r="L69" s="11" t="inlineStr"/>
-      <c r="M69" s="11" t="inlineStr"/>
-      <c r="N69" s="12" t="inlineStr"/>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>찬양대</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>3부 찬양대</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr"/>
+      <c r="L69" s="6" t="inlineStr"/>
+      <c r="M69" s="6" t="inlineStr"/>
+      <c r="N69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
@@ -2893,12 +2913,12 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>주일찬양</t>
+          <t>찬양대</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>2부</t>
+          <t>오후 찬양대</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2909,11 +2929,7 @@
       <c r="F70" s="8" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>주일찬양 봉사 시간대 중 택1</t>
-        </is>
-      </c>
+      <c r="I70" s="8" t="inlineStr"/>
       <c r="J70" s="8" t="inlineStr"/>
       <c r="K70" s="8" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
@@ -2931,12 +2947,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>주일찬양</t>
+          <t>찬양대</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>3부</t>
+          <t>수요오전 찬양대</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2947,11 +2963,7 @@
       <c r="F71" s="8" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr"/>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>주일찬양 봉사 시간대 중 택1</t>
-        </is>
-      </c>
+      <c r="I71" s="8" t="inlineStr"/>
       <c r="J71" s="8" t="inlineStr"/>
       <c r="K71" s="8" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
@@ -2969,12 +2981,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>주일찬양</t>
+          <t>찬양대</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>오후</t>
+          <t>수요오후 찬양대</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2985,11 +2997,7 @@
       <c r="F72" s="8" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>주일찬양 봉사 시간대 중 택1</t>
-        </is>
-      </c>
+      <c r="I72" s="8" t="inlineStr"/>
       <c r="J72" s="8" t="inlineStr"/>
       <c r="K72" s="8" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
@@ -3007,12 +3015,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>수요찬양</t>
+          <t>찬양대</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>오전</t>
+          <t>금요성령집회 찬양대</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3023,11 +3031,7 @@
       <c r="F73" s="8" t="inlineStr"/>
       <c r="G73" s="8" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>수요찬양 봉사 시간대 중 택1</t>
-        </is>
-      </c>
+      <c r="I73" s="8" t="inlineStr"/>
       <c r="J73" s="8" t="inlineStr"/>
       <c r="K73" s="8" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
@@ -3045,12 +3049,12 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>수요찬양</t>
+          <t>오케스트라</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>오후</t>
+          <t>베데스다</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -3058,14 +3062,14 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>2부</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>수요찬양 봉사 시간대 중 택1</t>
-        </is>
-      </c>
+      <c r="I74" s="8" t="inlineStr"/>
       <c r="J74" s="8" t="inlineStr"/>
       <c r="K74" s="8" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
@@ -3081,10 +3085,14 @@
           <t>찬양부</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr"/>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>오케스트라</t>
+        </is>
+      </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>금요성령집회찬양</t>
+          <t>비파와수금</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -3092,7 +3100,11 @@
           <t>신청가능</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>3부</t>
+        </is>
+      </c>
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="8" t="inlineStr"/>
@@ -3114,7 +3126,7 @@
       <c r="C76" s="6" t="inlineStr"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>중보기도팀(찬양)</t>
+          <t>중보기도팀</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -3133,146 +3145,130 @@
       <c r="N76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n">
+      <c r="A77" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>찬양부</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr"/>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>찬양대운영</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>임명직</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr"/>
-      <c r="G77" s="12" t="inlineStr"/>
-      <c r="H77" s="11" t="inlineStr"/>
-      <c r="I77" s="12" t="inlineStr"/>
-      <c r="J77" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 임명직으로 볼지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr"/>
-      <c r="L77" s="11" t="inlineStr"/>
-      <c r="M77" s="11" t="inlineStr"/>
-      <c r="N77" s="12" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>희망의복지재단(사회봉사센터)</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>봉사센터운영</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr"/>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
+      <c r="N77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="n">
+      <c r="A78" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>찬양부</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr"/>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>찬양팀운영</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>임명직</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="inlineStr"/>
-      <c r="G78" s="12" t="inlineStr"/>
-      <c r="H78" s="11" t="inlineStr"/>
-      <c r="I78" s="12" t="inlineStr"/>
-      <c r="J78" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 임명직으로 볼지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K78" s="12" t="inlineStr"/>
-      <c r="L78" s="11" t="inlineStr"/>
-      <c r="M78" s="11" t="inlineStr"/>
-      <c r="N78" s="12" t="inlineStr"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>희망의복지재단(사회봉사센터)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>희망푸드뱅크</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr"/>
+      <c r="G78" s="8" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr"/>
+      <c r="J78" s="8" t="inlineStr"/>
+      <c r="K78" s="8" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr"/>
+      <c r="M78" s="6" t="inlineStr"/>
+      <c r="N78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n">
+      <c r="A79" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>찬양부</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr"/>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>오케스트라</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="inlineStr"/>
-      <c r="G79" s="12" t="inlineStr"/>
-      <c r="H79" s="11" t="inlineStr"/>
-      <c r="I79" s="12" t="inlineStr"/>
-      <c r="J79" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 신청 대상 누락인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K79" s="12" t="inlineStr"/>
-      <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="11" t="inlineStr"/>
-      <c r="N79" s="12" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>희망의복지재단(사회봉사센터)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>사랑의봉사팀</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr"/>
+      <c r="K79" s="8" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr"/>
+      <c r="N79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="n">
+      <c r="A80" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>찬양부</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr"/>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>주나힘찬양</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="inlineStr"/>
-      <c r="G80" s="12" t="inlineStr"/>
-      <c r="H80" s="11" t="inlineStr"/>
-      <c r="I80" s="12" t="inlineStr"/>
-      <c r="J80" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에만 있고 신청서 양식에는 없음 — 신청 대상 누락인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K80" s="12" t="inlineStr"/>
-      <c r="L80" s="11" t="inlineStr"/>
-      <c r="M80" s="11" t="inlineStr"/>
-      <c r="N80" s="12" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>희망의복지재단(사회봉사센터)</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>도서관책마을</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr"/>
+      <c r="J80" s="8" t="inlineStr"/>
+      <c r="K80" s="8" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr"/>
+      <c r="M80" s="6" t="inlineStr"/>
+      <c r="N80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>희망의복지재단(사회봉사센터)</t>
         </is>
@@ -3280,7 +3276,7 @@
       <c r="C81" s="6" t="inlineStr"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>봉사센터운영</t>
+          <t>그루터기사역</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3302,15 +3298,15 @@
       <c r="A82" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>희망의복지재단(사회봉사센터)</t>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>L-12(목양부)</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>희망푸드뱅크</t>
+          <t>운영</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3334,13 +3330,13 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>희망의복지재단(사회봉사센터)</t>
+          <t>L-12(목양부)</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>사랑의봉사팀</t>
+          <t>목양지원</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -3359,226 +3355,226 @@
       <c r="N83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n">
+      <c r="A84" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>희망의복지재단(사회봉사센터)</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>도서관책마을</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr"/>
-      <c r="K84" s="8" t="inlineStr"/>
-      <c r="L84" s="6" t="inlineStr"/>
-      <c r="M84" s="6" t="inlineStr"/>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>L-12(목양부)</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr"/>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>정착관리</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr"/>
+      <c r="G84" s="12" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr"/>
+      <c r="I84" s="12" t="inlineStr"/>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>조직표(인사표)에는 '목양관리'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr"/>
+      <c r="L84" s="11" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr"/>
+      <c r="N84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n">
+      <c r="A85" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>희망의복지재단(사회봉사센터)</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>그루터기사역</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr"/>
-      <c r="G85" s="8" t="inlineStr"/>
-      <c r="H85" s="6" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr"/>
-      <c r="J85" s="8" t="inlineStr"/>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="6" t="inlineStr"/>
-      <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>L-12(목양부)</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr"/>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>소그룹 리더교육</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr"/>
+      <c r="G85" s="12" t="inlineStr"/>
+      <c r="H85" s="11" t="inlineStr"/>
+      <c r="I85" s="12" t="inlineStr"/>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>조직표(인사표)에는 '서기'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr"/>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
+      <c r="N85" s="12" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n">
+      <c r="A86" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>L-12(목양부)</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr"/>
-      <c r="G86" s="8" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr"/>
-      <c r="J86" s="8" t="inlineStr"/>
-      <c r="K86" s="8" t="inlineStr"/>
-      <c r="L86" s="6" t="inlineStr"/>
-      <c r="M86" s="6" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="C86" s="11" t="inlineStr"/>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>회계</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>임명직</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr"/>
+      <c r="G86" s="12" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="12" t="inlineStr"/>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>조직표(인사표)에만 있음 — 임명직인지 확인 필요</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr"/>
+      <c r="L86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr"/>
+      <c r="N86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n">
+      <c r="A87" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>L-12(목양부)</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr"/>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>목양지원</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr"/>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="6" t="inlineStr"/>
-      <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="C87" s="9" t="inlineStr"/>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>리더</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>임명직</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr"/>
+      <c r="G87" s="10" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr"/>
+      <c r="I87" s="10" t="inlineStr"/>
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n">
+      <c r="A88" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>L-12(목양부)</t>
-        </is>
-      </c>
-      <c r="C88" s="11" t="inlineStr"/>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>정착관리</t>
-        </is>
-      </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="inlineStr"/>
-      <c r="G88" s="12" t="inlineStr"/>
-      <c r="H88" s="11" t="inlineStr"/>
-      <c r="I88" s="12" t="inlineStr"/>
-      <c r="J88" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에는 '목양관리'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K88" s="12" t="inlineStr"/>
-      <c r="L88" s="11" t="inlineStr"/>
-      <c r="M88" s="11" t="inlineStr"/>
-      <c r="N88" s="12" t="inlineStr"/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>총무부</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr"/>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>대외협력</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr"/>
+      <c r="J88" s="8" t="inlineStr"/>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="6" t="inlineStr"/>
+      <c r="M88" s="6" t="inlineStr"/>
+      <c r="N88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n">
+      <c r="A89" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>L-12(목양부)</t>
-        </is>
-      </c>
-      <c r="C89" s="11" t="inlineStr"/>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>소그룹 리더교육</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="inlineStr"/>
-      <c r="G89" s="12" t="inlineStr"/>
-      <c r="H89" s="11" t="inlineStr"/>
-      <c r="I89" s="12" t="inlineStr"/>
-      <c r="J89" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에는 '서기'로 표기 — 같은 팀인지, 다른 팀인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K89" s="12" t="inlineStr"/>
-      <c r="L89" s="11" t="inlineStr"/>
-      <c r="M89" s="11" t="inlineStr"/>
-      <c r="N89" s="12" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>총무부</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr"/>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>역사홍보</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
+      <c r="J89" s="8" t="inlineStr"/>
+      <c r="K89" s="8" t="inlineStr"/>
+      <c r="L89" s="6" t="inlineStr"/>
+      <c r="M89" s="6" t="inlineStr"/>
+      <c r="N89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="n">
+      <c r="A90" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>L-12(목양부)</t>
-        </is>
-      </c>
-      <c r="C90" s="11" t="inlineStr"/>
-      <c r="D90" s="12" t="inlineStr">
-        <is>
-          <t>회계</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>임명직</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="inlineStr"/>
-      <c r="G90" s="12" t="inlineStr"/>
-      <c r="H90" s="11" t="inlineStr"/>
-      <c r="I90" s="12" t="inlineStr"/>
-      <c r="J90" s="12" t="inlineStr">
-        <is>
-          <t>조직표(인사표)에만 있음 — 임명직인지 확인 필요</t>
-        </is>
-      </c>
-      <c r="K90" s="12" t="inlineStr"/>
-      <c r="L90" s="11" t="inlineStr"/>
-      <c r="M90" s="11" t="inlineStr"/>
-      <c r="N90" s="12" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>총무부</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>경축부</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
+      <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="6" t="inlineStr"/>
+      <c r="M90" s="6" t="inlineStr"/>
+      <c r="N90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="9" t="n">
@@ -3586,13 +3582,13 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>L-12(목양부)</t>
+          <t>총무부</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr"/>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>리더</t>
+          <t>상담실</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -3616,13 +3612,13 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>총무부</t>
+          <t>시설부</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>대외협력</t>
+          <t>안전관리</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -3646,13 +3642,13 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>총무부</t>
+          <t>시설부</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>역사홍보</t>
+          <t>시설관리</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3676,13 +3672,13 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>총무부</t>
+          <t>시설부</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>경축부</t>
+          <t>자재관리</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3701,159 +3697,39 @@
       <c r="N94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="n">
+      <c r="A95" s="6" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>총무부</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr"/>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>상담실</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>임명직</t>
-        </is>
-      </c>
-      <c r="F95" s="10" t="inlineStr"/>
-      <c r="G95" s="10" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr"/>
-      <c r="I95" s="10" t="inlineStr"/>
-      <c r="J95" s="10" t="inlineStr"/>
-      <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="9" t="inlineStr"/>
-      <c r="M95" s="9" t="inlineStr"/>
-      <c r="N95" s="10" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>시설부</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>안전관리</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr"/>
-      <c r="K96" s="8" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr"/>
-      <c r="M96" s="6" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>시설부</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>시설관리</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F97" s="8" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr"/>
-      <c r="J97" s="8" t="inlineStr"/>
-      <c r="K97" s="8" t="inlineStr"/>
-      <c r="L97" s="6" t="inlineStr"/>
-      <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>시설부</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>자재관리</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr"/>
-      <c r="I98" s="8" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr"/>
-      <c r="L98" s="6" t="inlineStr"/>
-      <c r="M98" s="6" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>시설부</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr"/>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr"/>
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>데코</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>신청가능</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr"/>
-      <c r="G99" s="8" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr"/>
-      <c r="I99" s="8" t="inlineStr"/>
-      <c r="J99" s="8" t="inlineStr"/>
-      <c r="K99" s="8" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr"/>
-      <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>신청가능</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="6" t="inlineStr"/>
+      <c r="M95" s="6" t="inlineStr"/>
+      <c r="N95" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N99"/>
+  <autoFilter ref="A1:N95"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2:L99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
+    <dataValidation sqref="L2:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 골라주세요" prompt="유지 / 이름 수정 / 신설 / 폐지 중 선택" type="list">
       <formula1>"유지,이름 수정,신설,폐지"</formula1>
     </dataValidation>
   </dataValidations>

--- a/ministry/2026_사역신청_부서확인양식.xlsx
+++ b/ministry/2026_사역신청_부서확인양식.xlsx
@@ -2845,12 +2845,12 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>찬양대</t>
+          <t>찬양팀</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>2부 찬양대</t>
+          <t>2부 찬양팀</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>찬양대</t>
+          <t>찬양팀</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>3부 찬양대</t>
+          <t>3부 찬양팀</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>찬양대</t>
+          <t>찬양팀</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>오후 찬양대</t>
+          <t>오후 찬양팀</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>찬양대</t>
+          <t>찬양팀</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>수요오전 찬양대</t>
+          <t>수요오전 찬양팀</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>찬양대</t>
+          <t>찬양팀</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>수요오후 찬양대</t>
+          <t>수요오후 찬양팀</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>찬양대</t>
+          <t>찬양팀</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>금요성령집회 찬양대</t>
+          <t>금요성령집회 찬양팀</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
